--- a/outputs/CONDOMINIO_RESIDENCIAL_SPAZIO_CHELSEA_-_CNPJ__15.041.747_0001-65_000000_seens.xlsx
+++ b/outputs/CONDOMINIO_RESIDENCIAL_SPAZIO_CHELSEA_-_CNPJ__15.041.747_0001-65_000000_seens.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Balancete" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balancete" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A5:L89"/>
+  <dimension ref="A5:L88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="3" max="3"/>
@@ -481,7 +481,7 @@
     <row r="12">
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>TAXA DE CONDOMNIO - REF: 02/2026 - - COTA DO MS</t>
+          <t>TAXA DE CONDOMÍNIO - REF: 02/2026 - - COTA DO MÊS</t>
         </is>
       </c>
       <c r="L12" s="3" t="n">
@@ -491,7 +491,7 @@
     <row r="13">
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>RECEITA COM JUROS DA POUPANA / APLICAES - REF: 02/2026 - - RENTABILIDADE INVEST FCIL CREDITO MS</t>
+          <t>RECEITA COM JUROS DA POUPANÇA / APLICAÇÕES - REF: 02/2026 - - RENTABILIDADE INVEST FÁCIL CREDITO MÊS</t>
         </is>
       </c>
       <c r="L13" s="3" t="n">
@@ -528,7 +528,7 @@
     <row r="17">
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>DECLARACAO RECEITA DCTF/ENCARGOS (VALDECY VILELA) - - REFERENTE MS 02/2026 10/02/2026 PIX R$80,00 01/2026</t>
+          <t>DECLARACAO RECEITA DCTF/ENCARGOS (VALDECY VILELA) - - REFERENTE MÊS 02/2026 10/02/2026 PIX R$80,00 01/2026</t>
         </is>
       </c>
       <c r="L17" s="3" t="n">
@@ -538,7 +538,7 @@
     <row r="18">
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>DARF - PIS/ COFINS/ CSLL E INSS (MINISTERIO DA FAZENDA - RECEITA FEDERAL DO 02/2026 18/02/2026 BOLETO R$2.290,14 BRASIL) - - DARF UNIFICADA- RETENCES NF 09 MASTER TERCEIRIZADA E NF 1054 ATALS ELEVADORES</t>
+          <t>DARF - PIS/ COFINS/ CSLL E INSS (MINISTERIO DA FAZENDA - RECEITA FEDERAL DO 02/2026 18/02/2026 BOLETO R$2.290,14 BRASIL) - - DARF UNIFICADA- RETENCÕES NF 09 MASTER TERCEIRIZADA E NF 1054 ATALS ELEVADORES</t>
         </is>
       </c>
       <c r="L18" s="3" t="n">
@@ -558,7 +558,7 @@
     <row r="20">
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>(-) MANUTEN��O E CONSERVA��O</t>
+          <t>(-) MANUTENÇÃO E CONSERVAÇÃO</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
     <row r="23">
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>MANUTENO BOMBA / MOTOBOMBA DE RECALQUE/ PAINEL DE COMANDO (TEC 02/2026 03/02/2026 BOLETO 416 R$250,00 BOMBAS SERVICE - REPAROS EM EQUIPAMENTOS HIDRAULICOS LTDA) - - VISTORIA E REGULAGEM DO RELE TERMICO</t>
+          <t>MANUTENÇÃO BOMBA / MOTOBOMBA DE RECALQUE/ PAINEL DE COMANDO (TEC 02/2026 03/02/2026 BOLETO 416 R$250,00 BOMBAS SERVICE - REPAROS EM EQUIPAMENTOS HIDRAULICOS LTDA) - - VISTORIA E REGULAGEM DO RELE TERMICO</t>
         </is>
       </c>
       <c r="L23" s="3" t="n">
@@ -595,7 +595,7 @@
     <row r="24">
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIDRAARIA (ILSON JOSE MOURA VIEIRA - IDEAL VIDROS VIDRAARIA) - - AQUISIAO DE 02/2026 05/02/2026 PIX 20 R$725,00 UMA PORTA DE VIDRO TEMPERADA PARA CHURRASQUEIRA- ENTRADA 50%</t>
+          <t>VIDRAÇARIA (ILSON JOSE MOURA VIEIRA - IDEAL VIDROS VIDRAÇARIA) - - AQUISIÇAO DE 02/2026 05/02/2026 PIX 20 R$725,00 UMA PORTA DE VIDRO TEMPERADA PARA CHURRASQUEIRA- ENTRADA 50%</t>
         </is>
       </c>
       <c r="L24" s="3" t="n">
@@ -615,7 +615,7 @@
     <row r="26">
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>MANUTENO HIDRULICA (MACAGNAN COMERCIO DE MATERIAIS ELETRICOS LTDA) - - 02/2026 12/02/2026 PIX 1639 R$110,00 01 TORNEIRA ESFERA DE JARDIM E 1 ROLO DE FITA ZEBRADA</t>
+          <t>MANUTENÇÃO HIDRÁULICA (MACAGNAN COMERCIO DE MATERIAIS ELETRICOS LTDA) - - 02/2026 12/02/2026 PIX 1639 R$110,00 01 TORNEIRA ESFERA DE JARDIM E 1 ROLO DE FITA ZEBRADA</t>
         </is>
       </c>
       <c r="L26" s="3" t="n">
@@ -625,7 +625,7 @@
     <row r="27">
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>SISTEMA DE ALARME / CMERAS (MH SOLUCOES EM EQUIPAMENTOS DE SEGURANCA 02/2026 12/02/2026 BOLETO 1989 R$791,06 LTDA) - - SUBSTITUIO DO CONVERSOR DE VIDEO CFTV POWER BALUN INTELBRAS DA PORTARIA - REALIZADO EM 21/01/26 1/2</t>
+          <t>SISTEMA DE ALARME / CÂMERAS (MH SOLUCOES EM EQUIPAMENTOS DE SEGURANCA 02/2026 12/02/2026 BOLETO 1989 R$791,06 LTDA) - - SUBSTITUIÇÃO DO CONVERSOR DE VIDEO CFTV POWER BALUN INTELBRAS DA PORTARIA - REALIZADO EM 21/01/26 1/2</t>
         </is>
       </c>
       <c r="L27" s="3" t="n">
@@ -635,7 +635,7 @@
     <row r="28">
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>MANUTENO DIVERSAS (BETEL COMERCIO E MANUTENCAO DE FERRAMENTAS LTDA) - - 02/2026 12/02/2026 PIX 50 E R$958,00 MANUTENO DE 02 ROADEIRAS A GASOLINA 51</t>
+          <t>MANUTENÇÃO DIVERSAS (BETEL COMERCIO E MANUTENCAO DE FERRAMENTAS LTDA) - - 02/2026 12/02/2026 PIX 50 E R$958,00 MANUTENÇÃO DE 02 ROÇADEIRAS A GASOLINA 51</t>
         </is>
       </c>
       <c r="L28" s="3" t="n">
@@ -645,7 +645,7 @@
     <row r="29">
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIDRAARIA (ILSON JOSE MOURA VIEIRA - IDEAL VIDROS VIDRAARIA) - - AQUISIAO DE 02/2026 13/02/2026 PIX 20</t>
+          <t>VIDRAÇARIA (ILSON JOSE MOURA VIEIRA - IDEAL VIDROS VIDRAÇARIA) - - AQUISIÇAO DE 02/2026 13/02/2026 PIX 20</t>
         </is>
       </c>
       <c r="L29" s="3" t="n">
@@ -655,7 +655,7 @@
     <row r="30">
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>EMPRESA TERCEIRIZADA - LIMPEZA E CONSERVAO (ELIANE FOGACA SILVA DE 02/2026 13/02/2026 BOLETO 44 R$27.920,00 OLIVEIRA - TERCEIRIZADA LIMPEZA)</t>
+          <t>EMPRESA TERCEIRIZADA - LIMPEZA E CONSERVAÇÃO (ELIANE FOGACA SILVA DE 02/2026 13/02/2026 BOLETO 44 R$27.920,00 OLIVEIRA - TERCEIRIZADA LIMPEZA)</t>
         </is>
       </c>
       <c r="L30" s="3" t="n">
@@ -665,7 +665,7 @@
     <row r="31">
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>MANUTENO ELEVADORES (ATLAS SHINDLER) 02/2026 18/02/2026 BOLETO 3925</t>
+          <t>MANUTENÇÃO ELEVADORES (ATLAS SHINDLER) 02/2026 18/02/2026 BOLETO 3925</t>
         </is>
       </c>
       <c r="L31" s="3" t="n">
@@ -675,7 +675,7 @@
     <row r="32">
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>MANUTENO ELEVADORES (ATLAS SHINDLER) - - TROCA DE BOTO DA CABINA 02/2026 18/02/2026 BOLETO 1952</t>
+          <t>MANUTENÇÃO ELEVADORES (ATLAS SHINDLER) - - TROCA DE BOTÃO DA CABINA 02/2026 18/02/2026 BOLETO 1952</t>
         </is>
       </c>
       <c r="L32" s="3" t="n">
@@ -695,7 +695,7 @@
     <row r="34">
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>MANUTENO SPDA (INSTALAPAR SPDA LTDA.) - MANUTENO ANUAL PARA RAIO 02/2026 18/02/2026 BOLETO 1535</t>
+          <t>MANUTENÇÃO SPDA (INSTALAPAR SPDA LTDA.) - MANUTENÇÃO ANUAL PARA RAIO 02/2026 18/02/2026 BOLETO 1535</t>
         </is>
       </c>
       <c r="L34" s="3" t="n">
@@ -705,7 +705,7 @@
     <row r="35">
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>EMPRESA TERCEIRIZADA - LIMPEZA E CONSERVAO (MASTER FACILITIES - SERVICOS 02/2026 23/02/2026 BOLETO 226 R$10.837,78 TERCEIRIZADOS LTDA)</t>
+          <t>EMPRESA TERCEIRIZADA - LIMPEZA E CONSERVAÇÃO (MASTER FACILITIES - SERVICOS 02/2026 23/02/2026 BOLETO 226 R$10.837,78 TERCEIRIZADOS LTDA)</t>
         </is>
       </c>
       <c r="L35" s="3" t="n">
@@ -715,7 +715,7 @@
     <row r="36">
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>MANUTENO ACESSO REMOTO FACIAL / SISTEMA CONTROLE DE ACESSO (MH 02/2026 23/02/2026 BOLETO 2028 R$380,00 SOLUCOES EM EQUIPAMENTOS DE SEGURANCA LTDA) - - ATENDIMENTO EMERGENCIAL NOTURNO PARA MANUTENAO DE CONTROLE DE ACESSO BL 01 - PORTA TRAVADA - REALIZADO EM 29/01/26</t>
+          <t>MANUTENÇÃO ACESSO REMOTO FACIAL / SISTEMA CONTROLE DE ACESSO (MH 02/2026 23/02/2026 BOLETO 2028 R$380,00 SOLUCOES EM EQUIPAMENTOS DE SEGURANCA LTDA) - - ATENDIMENTO EMERGENCIAL NOTURNO PARA MANUTENÇAO DE CONTROLE DE ACESSO BL 01 - PORTA TRAVADA - REALIZADO EM 29/01/26</t>
         </is>
       </c>
       <c r="L36" s="3" t="n">
@@ -735,14 +735,14 @@
     <row r="38">
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>(-) SERVI�OS P�BLICOS</t>
+          <t>(-) SERVIÇOS PÚBLICOS</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>ENERGIA ELTRICA (COPEL DISTRIBUIAO S/A) - - UNIDADE CONSUMIDORA 91487285 02/2026 18/02/2026 BOLETO</t>
+          <t>ENERGIA ELÉTRICA (COPEL DISTRIBUIÇAO S/A) - - UNIDADE CONSUMIDORA 91487285 02/2026 18/02/2026 BOLETO</t>
         </is>
       </c>
       <c r="L39" s="3" t="n">
@@ -762,7 +762,7 @@
     <row r="41">
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>GUA E ESGOTO (COMPANHIA DE SANEAMENTO DO PARANA SANEPAR) - - MATRICULA 02/2026 25/02/2026 DBITO R$17.777,28 30266110 PGINA 1 / 3 AUTOMTICO</t>
+          <t>ÁGUA E ESGOTO (COMPANHIA DE SANEAMENTO DO PARANA SANEPAR) - - MATRICULA 02/2026 25/02/2026 DÉBITO R$17.777,28 30266110 PÁGINA 1 / 3 AUTOMÁTICO</t>
         </is>
       </c>
       <c r="L41" s="3" t="n">
@@ -772,7 +772,7 @@
     <row r="42">
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>TELEFONE / INTERNET (CLARO NXT TELECOMUNICACOES S/A) 02/2026 25/02/2026 DBITO R$137,59 AUTOMTICO</t>
+          <t>TELEFONE / INTERNET (CLARO NXT TELECOMUNICACOES S/A) 02/2026 25/02/2026 DÉBITO R$137,59 AUTOMÁTICO</t>
         </is>
       </c>
       <c r="L42" s="3" t="n">
@@ -792,14 +792,14 @@
     <row r="44">
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>(-) SERVI�OS FINANCEIROS</t>
+          <t>(-) SERVIÇOS FINANCEIROS</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>- NET EMPRESA) - - CESTA EMPRESARIAL 02/2026 13/02/2026 DBITO R$177,05 AUTOMTICO</t>
+          <t>- NET EMPRESA) - - CESTA EMPRESARIAL 02/2026 13/02/2026 DÉBITO R$177,05 AUTOMÁTICO</t>
         </is>
       </c>
       <c r="L45" s="3" t="n">
@@ -809,7 +809,7 @@
     <row r="46">
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>- NET EMPRESA) - - TARIFA TRANSFERNCIA 02/2026 24/02/2026 DBITO R$82,60 PIX AUTOMTICO</t>
+          <t>- NET EMPRESA) - - TARIFA TRANSFERÊNCIA 02/2026 24/02/2026 DÉBITO R$82,60 PIX AUTOMÁTICO</t>
         </is>
       </c>
       <c r="L46" s="3" t="n">
@@ -819,7 +819,7 @@
     <row r="47">
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>- NET EMPRESA) - - IOF INVEST FACIL 02/2026 25/02/2026 DBITO R$7,08 AUTOMTICO</t>
+          <t>- NET EMPRESA) - - IOF INVEST FACIL 02/2026 25/02/2026 DÉBITO R$7,08 AUTOMÁTICO</t>
         </is>
       </c>
       <c r="L47" s="3" t="n">
@@ -846,7 +846,7 @@
     <row r="50">
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>HONORRIOS SNDICO PROFISSIONAL (G.K.B. SINDICOS E ADMINISTRACAO DE 02/2026 03/02/2026 PIX 26 R$3.242,00 CONDOMINIOS LTDA)</t>
+          <t>HONORÁRIOS SÍNDICO PROFISSIONAL (G.K.B. SINDICOS E ADMINISTRACAO DE 02/2026 03/02/2026 PIX 26 R$3.242,00 CONDOMINIOS LTDA)</t>
         </is>
       </c>
       <c r="L50" s="3" t="n">
@@ -856,7 +856,7 @@
     <row r="51">
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>HONORRIO SUB-SINDICA (CAMILA BARBOSA) 02/2026 03/02/2026 PIX</t>
+          <t>HONORÁRIO SUB-SINDICA (CAMILA BARBOSA) 02/2026 03/02/2026 PIX</t>
         </is>
       </c>
       <c r="L51" s="3" t="n">
@@ -866,7 +866,7 @@
     <row r="52">
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>HONORRIO SUB-SINDICA (BRUNA MOUSSA DAYOUB) 02/2026 03/02/2026 PIX</t>
+          <t>HONORÁRIO SUB-SINDICA (BRUNA MOUSSA DAYOUB) 02/2026 03/02/2026 PIX</t>
         </is>
       </c>
       <c r="L52" s="3" t="n">
@@ -876,7 +876,7 @@
     <row r="53">
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>- BAVATOS) - - 02/2026 04/02/2026 PIX 6723 R$16,00 ENCADERNAES LIVRO DE PRESTAO DE CONTAS</t>
+          <t>- BAVATOS) - - 02/2026 04/02/2026 PIX 6723 R$16,00 ENCADERNAÇÕES LIVRO DE PRESTAÇÃO DE CONTAS</t>
         </is>
       </c>
       <c r="L53" s="3" t="n">
@@ -896,7 +896,7 @@
     <row r="55">
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>- BAVATOS) - - 02/2026 20/02/2026 PIX 6808 R$7,00 ENCADERNAES LIVROS DE PRESTAO DE CONTAS</t>
+          <t>- BAVATOS) - - 02/2026 20/02/2026 PIX 6808 R$7,00 ENCADERNAÇÕES LIVROS DE PRESTAÇÃO DE CONTAS</t>
         </is>
       </c>
       <c r="L55" s="3" t="n">
@@ -916,14 +916,14 @@
     <row r="57">
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>(-) DESPESAS EXTRAORDIN�RIAS</t>
+          <t>(-) DESPESAS EXTRAORDINÁRIAS</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>SERVIO MOTOBOY (PABLO ARIEL DE OLIVEIRA - MOTOBOY) - - PEGAR SOPRADOR DE GRAMA 02/2026 05/02/2026 PIX R$15,00 NO CONDOMINIO E LEVAR NA ASSISTENCIA TECNICA CASSEL</t>
+          <t>SERVIÇO MOTOBOY (PABLO ARIEL DE OLIVEIRA - MOTOBOY) - - PEGAR SOPRADOR DE GRAMA 02/2026 05/02/2026 PIX R$15,00 NO CONDOMINIO E LEVAR NA ASSISTENCIA TECNICA CASSEL</t>
         </is>
       </c>
       <c r="L58" s="3" t="n">
@@ -933,7 +933,7 @@
     <row r="59">
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>LOCAO DE BENS MVEIS (BTTF55 COMERCIO E DISTRIBUICAO DE PURIFICADORES DE 02/2026 12/02/2026 BOLETO R$1.298,15 AGUA LTDA- PURIFICATTA) - - MQUINA PURIFICATTA- GUA FILTRADA</t>
+          <t>LOCAÇÃO DE BENS MÓVEIS (BTTF55 COMERCIO E DISTRIBUICAO DE PURIFICADORES DE 02/2026 12/02/2026 BOLETO R$1.298,15 AGUA LTDA- PURIFICATTA) - - MÁQUINA PURIFICATTA- ÁGUA FILTRADA</t>
         </is>
       </c>
       <c r="L59" s="3" t="n">
@@ -943,7 +943,7 @@
     <row r="60">
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>SERVIO MOTOBOY (PABLO ARIEL DE OLIVEIRA - MOTOBOY) - - ENTREGAR NO CONDOMINIO 02/2026 18/02/2026 PIX R$20,00 EDTIAL DE CONVOCAO E CINTO NOVO DA ROADEIRA</t>
+          <t>SERVIÇO MOTOBOY (PABLO ARIEL DE OLIVEIRA - MOTOBOY) - - ENTREGAR NO CONDOMINIO 02/2026 18/02/2026 PIX R$20,00 EDTIAL DE CONVOCAÇÃO E CINTO NOVO DA ROÇADEIRA</t>
         </is>
       </c>
       <c r="L60" s="3" t="n">
@@ -953,7 +953,7 @@
     <row r="61">
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>SERVIO MOTOBOY (PABLO ARIEL DE OLIVEIRA - MOTOBOY) - - RETIRAR 02 ROADEIRAS NA 02/2026 18/02/2026 PIX R$35,00 ASSISTENCIA TECNICA CASSEL E DEIXAR NO CONDOMINIO.</t>
+          <t>SERVIÇO MOTOBOY (PABLO ARIEL DE OLIVEIRA - MOTOBOY) - - RETIRAR 02 ROÇADEIRAS NA 02/2026 18/02/2026 PIX R$35,00 ASSISTENCIA TECNICA CASSEL E DEIXAR NO CONDOMINIO.</t>
         </is>
       </c>
       <c r="L61" s="3" t="n">
@@ -963,7 +963,7 @@
     <row r="62">
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>DESPESAS DIVERSAS (GEOVANI KARPSTEIN BAZELLA) - - AQUISIO DE GASOLINA PARA 02/2026 20/02/2026 PIX R$90,00 MAQUINA ROADEIRA COM 2 GALES PARA COMBUSTIVEIS- REEMBOLSO SINDICO</t>
+          <t>DESPESAS DIVERSAS (GEOVANI KARPSTEIN BAZELLA) - - AQUISIÇÃO DE GASOLINA PARA 02/2026 20/02/2026 PIX R$90,00 MAQUINA ROÇADEIRA COM 2 GALÕES PARA COMBUSTIVEIS- REEMBOLSO SINDICO</t>
         </is>
       </c>
       <c r="L62" s="3" t="n">
@@ -990,7 +990,7 @@
     <row r="65">
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>ABASTECIMENTO DE GS (SUPERGASBRAS ENERGIA LTDA) 02/2026 18/02/2026 BOLETO</t>
+          <t>ABASTECIMENTO DE GÁS (SUPERGASBRAS ENERGIA LTDA) 02/2026 18/02/2026 BOLETO</t>
         </is>
       </c>
       <c r="L65" s="3" t="n">
@@ -1074,41 +1074,44 @@
     <row r="74">
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>LANÇAMENTOS</t>
+          <t>FUNDO DE OBRA</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>FUNDO DE OBRA</t>
-        </is>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>SALDO ANTERIOR</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>SALDO ANTERIOR</t>
+          <t>ENTRADAS</t>
         </is>
       </c>
       <c r="L76" s="3" t="n">
-        <v>0</v>
+        <v>39188.8</v>
       </c>
     </row>
     <row r="77">
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>ENTRADAS</t>
+          <t>SAÍDAS</t>
         </is>
       </c>
       <c r="L77" s="3" t="n">
-        <v>39188.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>SAÍDAS</t>
+          <t>SALDO ATUAL</t>
         </is>
       </c>
       <c r="L78" s="3" t="n">
@@ -1116,46 +1119,46 @@
       </c>
     </row>
     <row r="79">
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>SALDO ATUAL</t>
-        </is>
-      </c>
-      <c r="L79" s="3" t="n">
+      <c r="C79" s="1" t="inlineStr">
+        <is>
+          <t>FUNDO DE RESERVA DE POUPANÇA PERMANENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>SALDO ANTERIOR</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>FUNDO DE RESERVA DE POUPANÇA PERMANENTE</t>
-        </is>
       </c>
     </row>
     <row r="81">
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>SALDO ANTERIOR</t>
+          <t>ENTRADAS</t>
         </is>
       </c>
       <c r="L81" s="3" t="n">
-        <v>0</v>
+        <v>43107.68</v>
       </c>
     </row>
     <row r="82">
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>ENTRADAS</t>
+          <t>SAÍDAS</t>
         </is>
       </c>
       <c r="L82" s="3" t="n">
-        <v>43107.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>SAÍDAS</t>
+          <t>SALDO ATUAL</t>
         </is>
       </c>
       <c r="L83" s="3" t="n">
@@ -1163,59 +1166,49 @@
       </c>
     </row>
     <row r="84">
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>SALDO ATUAL</t>
-        </is>
-      </c>
-      <c r="L84" s="3" t="n">
+      <c r="C84" s="1" t="inlineStr">
+        <is>
+          <t>CONTA CORRENTE - FLUXO DE CAIXA DE MANUTENÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>SALDO ANTERIOR</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>CONTA CORRENTE - FLUXO DE CAIXA DE MANUTENÇÃO</t>
-        </is>
       </c>
     </row>
     <row r="86">
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>SALDO ANTERIOR</t>
+          <t>ENTRADAS</t>
         </is>
       </c>
       <c r="L86" s="3" t="n">
-        <v>0</v>
+        <v>5847.29</v>
       </c>
     </row>
     <row r="87">
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>ENTRADAS</t>
+          <t>SAÍDAS</t>
         </is>
       </c>
       <c r="L87" s="3" t="n">
-        <v>5847.29</v>
+        <v>78296.42</v>
       </c>
     </row>
     <row r="88">
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>SAÍDAS</t>
+          <t>SALDO ATUAL</t>
         </is>
       </c>
       <c r="L88" s="3" t="n">
-        <v>78296.42</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>SALDO ATUAL</t>
-        </is>
-      </c>
-      <c r="L89" s="3" t="n">
         <v>0</v>
       </c>
     </row>
